--- a/live_sim_events_v3.xlsx
+++ b/live_sim_events_v3.xlsx
@@ -322,7 +322,7 @@
     <t>STPAC, LWPAC, RWPAC, CAMRD, CMBTB, LWDRB, RWDRB, RBPAC, LBPAC, STPRF</t>
   </si>
   <si>
-    <t>"he curls it towards the far post... Gooooooal! Wow! What a stunner! Not a piece of paper could have fit between the ball and the post! No one is saving that!... That was certainly one for the highlight reels, xy (player's team) are over the moon with that." (only if it's a goal that puts them ahead, or is a late (last 10 min) equalizer)</t>
+    <t>"he curls it towards the far post... Gooooooal! Wow! What a stunner! Not a piece of paper could have fit between the ball and the post! No one is saving that!... That was certainly one for the highlight reels, xy (player's team) are over the moon with that."</t>
   </si>
   <si>
     <t>D</t>
